--- a/results/link-prediction-gcn/Link/0shot/PTC_MR/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/0shot/PTC_MR/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.4677±0.0924</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.5801±0.0253</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.5800±0.0259</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5805±0.0247</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.5544±0.0316</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.5569±0.0264</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5494±0.0370</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5567±0.0292</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5567±0.0292</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5567±0.0292</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5304±0.0094</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5085±0.0188</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5393±0.0160</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.4021±0.0003</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5684±0.0429</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5697±0.0405</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5360±0.0728</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5857±0.0204</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.5596±0.0223</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5531±0.0358</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>0.5983±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>0.5983±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>0.5983±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.5976±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.5976±0.0000</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.5765±0.0000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5988±0.0007</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5487±0.0348</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5983±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.5995±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5924±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5586±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.4017±0.0000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5124±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.5976±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.5981±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.5816±0.0000</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.5599±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5976±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.5976±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.5983±0.0000</t>
-        </is>
-      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0003</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5699±0.0000</t>
+          <t>0.5584±0.0120</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.5889±0.0095</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5667±0.0294</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5261±0.0000</t>
+          <t>0.5703±0.0203</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5709±0.0000</t>
+          <t>0.5510±0.0369</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5900±0.0000</t>
+          <t>0.5450±0.0244</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.5229±0.0128</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.5229±0.0128</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.5229±0.0128</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5912±0.0000</t>
+          <t>0.5454±0.0366</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5254±0.0000</t>
+          <t>0.5032±0.0087</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5941±0.0000</t>
+          <t>0.5574±0.0248</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4677±0.0924</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5657±0.0000</t>
+          <t>0.5190±0.0117</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5857±0.0091</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5649±0.0293</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.5861±0.0182</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5550±0.0000</t>
+          <t>0.5541±0.0155</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5486±0.0000</t>
+          <t>0.5795±0.0076</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5266±0.0000</t>
+          <t>0.5091±0.0182</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5266±0.0000</t>
+          <t>0.5091±0.0182</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5266±0.0000</t>
+          <t>0.5091±0.0182</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5711±0.0000</t>
+          <t>0.5766±0.0025</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.4965±0.0000</t>
+          <t>0.5221±0.0141</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5302±0.0000</t>
+          <t>0.5261±0.0033</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0003</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5445±0.0144</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5970±0.0005</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5478±0.0235</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5557±0.0000</t>
+          <t>0.5798±0.0178</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5571±0.0294</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5572±0.0313</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5611±0.0162</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5611±0.0162</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5611±0.0162</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5292±0.0097</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5692±0.0000</t>
+          <t>0.5665±0.0266</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5619±0.0269</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4021±0.0003</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5343±0.0195</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.5870±0.0110</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5954±0.0031</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5964±0.0043</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5866±0.0136</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.5525±0.0345</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5862±0.0132</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5815±0.0217</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5973±0.0016</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5616±0.0000</t>
+          <t>0.5774±0.0296</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5361±0.0000</t>
+          <t>0.5408±0.0158</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5973±0.0007</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4017±0.0000</t>
+          <t>0.4672±0.0922</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5279±0.0000</t>
+          <t>0.5219±0.0033</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5214±0.0000</t>
+          <t>0.5729±0.0242</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5456±0.0533</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5279±0.0000</t>
+          <t>0.5716±0.0308</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5870±0.0085</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5367±0.0000</t>
+          <t>0.5308±0.0102</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5167±0.0190</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5167±0.0190</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5225±0.0000</t>
+          <t>0.5167±0.0190</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5302±0.0000</t>
+          <t>0.5364±0.0166</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5012±0.0144</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5296±0.0000</t>
+          <t>0.5243±0.0092</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.2496±0.3529</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.7277±0.0293</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.7279±0.0295</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.7289±0.0276</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.6960±0.0377</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.6934±0.0500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6766±0.0572</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6743±0.0520</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6743±0.0520</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6743±0.0520</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6524±0.0215</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6020±0.0327</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6496±0.0197</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6997±0.0697</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.7235±0.0357</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6875±0.0727</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.7322±0.0246</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.6976±0.0394</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6768±0.0579</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>0.7487±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.7487±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.7487±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.7289±0.0000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7491±0.0005</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.6650±0.0593</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.7487±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.7493±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.7440±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7142±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6730±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>0.7322±0.0000</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6810±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0438</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.7407±0.0076</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.7140±0.0359</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.7170±0.0269</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6890±0.0544</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6662±0.0470</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6409±0.0184</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6409±0.0184</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6409±0.0184</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6825±0.0462</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6190±0.0089</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0379</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.2496±0.3529</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.6109±0.0157</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.7379±0.0077</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.7187±0.0268</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.7298±0.0271</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6973±0.0265</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7253±0.0051</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6259±0.0127</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6259±0.0127</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.6259±0.0127</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7199±0.0009</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6279±0.0200</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6393±0.0076</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.7227±0.0000</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.7459±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.6785±0.0000</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0.7240±0.0000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.7414±0.0000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7444±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7444±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7444±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>0.7423±0.0000</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6228±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7454±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6443±0.0268</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.7477±0.0004</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.7041±0.0203</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.7320±0.0147</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.6852±0.0476</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.7047±0.0312</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.7102±0.0139</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7102±0.0139</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7102±0.0139</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6404±0.0147</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6879±0.0492</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.7142±0.0250</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6806±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.7472±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.7121±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6993±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.6732±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.6732±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.6732±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7224±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.5935±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.6678±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.7476±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.7118±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.7487±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.7437±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6878±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7481±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.6311±0.0202</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7390±0.0097</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7464±0.0025</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7465±0.0043</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7370±0.0135</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7336±0.0000</t>
+          <t>0.6827±0.0562</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7317±0.0209</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7308±0.0236</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7463±0.0000</t>
+          <t>0.7478±0.0012</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7114±0.0000</t>
+          <t>0.7141±0.0489</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6512±0.0000</t>
+          <t>0.6548±0.0160</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7473±0.0013</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.2494±0.3527</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6259±0.0000</t>
+          <t>0.6388±0.0051</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6814±0.0000</t>
+          <t>0.7246±0.0240</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7192±0.0000</t>
+          <t>0.6868±0.0683</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6790±0.0000</t>
+          <t>0.7182±0.0235</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.7388±0.0071</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6700±0.0000</t>
+          <t>0.6661±0.0075</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.6598±0.0135</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.6598±0.0135</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.6598±0.0135</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6678±0.0000</t>
+          <t>0.6714±0.0155</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6376±0.0000</t>
+          <t>0.5919±0.0116</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6616±0.0000</t>
+          <t>0.6636±0.0100</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4843±0.0000</t>
+          <t>0.7292±0.0269</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4747±0.0000</t>
+          <t>0.5024±0.0219</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4921±0.0000</t>
+          <t>0.4976±0.0044</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4859±0.0000</t>
+          <t>0.5294±0.0519</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.4940±0.0000</t>
+          <t>0.5121±0.0250</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.5140±0.0221</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4746±0.0000</t>
+          <t>0.5052±0.0260</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.4754±0.0000</t>
+          <t>0.5173±0.0183</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.4754±0.0000</t>
+          <t>0.5173±0.0183</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.4754±0.0000</t>
+          <t>0.5173±0.0183</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.4737±0.0000</t>
+          <t>0.5297±0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.4865±0.0000</t>
+          <t>0.4642±0.0093</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5156±0.0000</t>
+          <t>0.5390±0.0108</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.7061±0.0000</t>
+          <t>0.6983±0.0110</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.4973±0.0000</t>
+          <t>0.5228±0.0210</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4167±0.0000</t>
+          <t>0.4678±0.0435</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.4375±0.0000</t>
+          <t>0.4924±0.1028</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.4693±0.0000</t>
+          <t>0.5010±0.0300</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.4767±0.0000</t>
+          <t>0.5391±0.0649</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.5521±0.0000</t>
+          <t>0.5511±0.0221</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5738±0.0058</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5738±0.0058</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5738±0.0058</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.5295±0.0000</t>
+          <t>0.5705±0.0152</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4598±0.0000</t>
+          <t>0.4845±0.0139</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.5781±0.0000</t>
+          <t>0.5882±0.0086</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.7261±0.0000</t>
+          <t>0.6733±0.0132</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.4970±0.0000</t>
+          <t>0.5338±0.0342</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4960±0.0000</t>
+          <t>0.4881±0.0130</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.4876±0.0000</t>
+          <t>0.4698±0.0341</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.5044±0.0000</t>
+          <t>0.5601±0.0348</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5058±0.0000</t>
+          <t>0.4974±0.0266</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5072±0.0000</t>
+          <t>0.5275±0.0136</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5117±0.0074</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5117±0.0074</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5200±0.0000</t>
+          <t>0.5117±0.0074</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5077±0.0000</t>
+          <t>0.5119±0.0153</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4892±0.0000</t>
+          <t>0.4572±0.0026</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5305±0.0000</t>
+          <t>0.5482±0.0087</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6218±0.0000</t>
+          <t>0.5827±0.0592</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.5316±0.0000</t>
+          <t>0.5200±0.0076</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4931±0.0000</t>
+          <t>0.4888±0.0069</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4807±0.0000</t>
+          <t>0.4990±0.0834</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5549±0.0000</t>
+          <t>0.4875±0.0191</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5455±0.0000</t>
+          <t>0.5079±0.0086</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.5184±0.0000</t>
+          <t>0.5373±0.0249</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.4782±0.0000</t>
+          <t>0.5082±0.0189</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.4782±0.0000</t>
+          <t>0.5082±0.0189</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.4782±0.0000</t>
+          <t>0.5082±0.0189</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.5519±0.0000</t>
+          <t>0.5371±0.0199</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.4669±0.0000</t>
+          <t>0.4939±0.0123</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.4854±0.0000</t>
+          <t>0.5218±0.0112</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6800±0.0000</t>
+          <t>0.7173±0.0265</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.4696±0.0000</t>
+          <t>0.5390±0.0052</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4965±0.0000</t>
+          <t>0.5360±0.0531</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4960±0.0000</t>
+          <t>0.5640±0.1101</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.5477±0.0000</t>
+          <t>0.5423±0.0248</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5813±0.0000</t>
+          <t>0.5379±0.0320</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5059±0.0000</t>
+          <t>0.5225±0.0159</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.5135±0.0000</t>
+          <t>0.5829±0.0008</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.5135±0.0000</t>
+          <t>0.5829±0.0008</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.5135±0.0000</t>
+          <t>0.5829±0.0008</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5159±0.0000</t>
+          <t>0.5458±0.0077</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5012±0.0000</t>
+          <t>0.4994±0.0144</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.4938±0.0000</t>
+          <t>0.5478±0.0202</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7270±0.0000</t>
+          <t>0.7112±0.0127</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.4730±0.0000</t>
+          <t>0.5302±0.0186</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.4950±0.0000</t>
+          <t>0.5013±0.0367</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.4970±0.0000</t>
+          <t>0.5333±0.0783</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.5729±0.0000</t>
+          <t>0.5613±0.0161</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.4933±0.0000</t>
+          <t>0.5515±0.0212</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5261±0.0000</t>
+          <t>0.5222±0.0043</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5708±0.0000</t>
+          <t>0.5530±0.0157</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5709±0.0000</t>
+          <t>0.5683±0.0074</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5709±0.0000</t>
+          <t>0.5561±0.0150</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5176±0.0000</t>
+          <t>0.5382±0.0019</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.5080±0.0000</t>
+          <t>0.4956±0.0090</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.5972±0.0000</t>
+          <t>0.5586±0.0322</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6594±0.0000</t>
+          <t>0.6284±0.0939</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5197±0.0000</t>
+          <t>0.5144±0.0133</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4200±0.0000</t>
+          <t>0.4255±0.0097</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4090±0.0000</t>
+          <t>0.4084±0.0081</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.4891±0.0000</t>
+          <t>0.4914±0.0414</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.4454±0.0000</t>
+          <t>0.4958±0.0179</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5172±0.0000</t>
+          <t>0.5163±0.0178</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.4768±0.0000</t>
+          <t>0.4745±0.0409</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.4768±0.0000</t>
+          <t>0.4745±0.0409</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.4768±0.0000</t>
+          <t>0.4745±0.0409</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5156±0.0000</t>
+          <t>0.5272±0.0074</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.4703±0.0000</t>
+          <t>0.4806±0.0131</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.4928±0.0000</t>
+          <t>0.5168±0.0068</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5888±0.0000</t>
+          <t>0.7614±0.0156</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5638±0.0000</t>
+          <t>0.5965±0.0328</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5945±0.0000</t>
+          <t>0.6058±0.0140</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5908±0.0000</t>
+          <t>0.6266±0.0454</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5929±0.0000</t>
+          <t>0.6009±0.0156</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6258±0.0000</t>
+          <t>0.6151±0.0182</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.5694±0.0000</t>
+          <t>0.6082±0.0286</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5628±0.0000</t>
+          <t>0.6043±0.0330</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5631±0.0000</t>
+          <t>0.6043±0.0330</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5631±0.0000</t>
+          <t>0.6042±0.0330</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5697±0.0000</t>
+          <t>0.6378±0.0136</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5939±0.0000</t>
+          <t>0.5760±0.0095</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6053±0.0000</t>
+          <t>0.6404±0.0130</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7554±0.0000</t>
+          <t>0.7378±0.0201</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.5834±0.0000</t>
+          <t>0.6143±0.0239</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5564±0.0000</t>
+          <t>0.5822±0.0219</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5667±0.0000</t>
+          <t>0.6138±0.0796</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5615±0.0000</t>
+          <t>0.5859±0.0269</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.5716±0.0000</t>
+          <t>0.6305±0.0641</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6569±0.0000</t>
+          <t>0.6481±0.0115</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.6463±0.0077</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.6463±0.0077</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.6463±0.0077</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6480±0.0000</t>
+          <t>0.6561±0.0121</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5772±0.0000</t>
+          <t>0.5916±0.0091</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6461±0.0000</t>
+          <t>0.6577±0.0082</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7271±0.0102</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.5837±0.0000</t>
+          <t>0.6218±0.0334</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.5926±0.0063</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5852±0.0350</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6016±0.0000</t>
+          <t>0.6400±0.0331</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.5813±0.0000</t>
+          <t>0.6100±0.0426</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.5868±0.0000</t>
+          <t>0.6219±0.0304</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5972±0.0000</t>
+          <t>0.6253±0.0027</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5972±0.0000</t>
+          <t>0.6251±0.0027</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5972±0.0000</t>
+          <t>0.6252±0.0028</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5871±0.0000</t>
+          <t>0.6111±0.0251</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5888±0.0000</t>
+          <t>0.5671±0.0043</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6118±0.0000</t>
+          <t>0.6431±0.0049</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7073±0.0000</t>
+          <t>0.6614±0.0560</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6242±0.0000</t>
+          <t>0.6341±0.0053</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5950±0.0000</t>
+          <t>0.5929±0.0033</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5891±0.0000</t>
+          <t>0.6226±0.0768</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6451±0.0000</t>
+          <t>0.5979±0.0335</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6471±0.0000</t>
+          <t>0.6017±0.0048</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5973±0.0000</t>
+          <t>0.6131±0.0193</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6299±0.0115</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6299±0.0115</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6299±0.0115</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6134±0.0000</t>
+          <t>0.6283±0.0154</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5804±0.0000</t>
+          <t>0.5924±0.0094</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5956±0.0000</t>
+          <t>0.6280±0.0045</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7396±0.0000</t>
+          <t>0.7484±0.0064</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.5606±0.0000</t>
+          <t>0.6525±0.0117</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5952±0.0000</t>
+          <t>0.6365±0.0565</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6755±0.0885</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6438±0.0000</t>
+          <t>0.6410±0.0206</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6843±0.0000</t>
+          <t>0.6398±0.0342</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.5946±0.0000</t>
+          <t>0.6118±0.0144</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6246±0.0000</t>
+          <t>0.7011±0.0029</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6246±0.0000</t>
+          <t>0.7011±0.0029</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6246±0.0000</t>
+          <t>0.7011±0.0029</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6020±0.0000</t>
+          <t>0.6554±0.0041</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5986±0.0000</t>
+          <t>0.5996±0.0065</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.5901±0.0000</t>
+          <t>0.6485±0.0346</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7684±0.0000</t>
+          <t>0.7405±0.0217</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.5657±0.0000</t>
+          <t>0.6388±0.0061</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.6119±0.0364</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.6325±0.0641</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6450±0.0000</t>
+          <t>0.6290±0.0114</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.5610±0.0000</t>
+          <t>0.6473±0.0282</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6128±0.0000</t>
+          <t>0.6175±0.0106</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6325±0.0372</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6669±0.0314</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6609±0.0170</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.5992±0.0000</t>
+          <t>0.6197±0.0208</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5935±0.0076</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6327±0.0000</t>
+          <t>0.6332±0.0179</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7432±0.0000</t>
+          <t>0.7052±0.0768</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.6380±0.0000</t>
+          <t>0.6258±0.0138</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5603±0.0000</t>
+          <t>0.5588±0.0046</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5519±0.0000</t>
+          <t>0.5506±0.0056</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6026±0.0000</t>
+          <t>0.5836±0.0386</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5269±0.0000</t>
+          <t>0.5816±0.0240</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6273±0.0000</t>
+          <t>0.6131±0.0168</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5819±0.0228</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5819±0.0228</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5819±0.0228</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.6183±0.0000</t>
+          <t>0.6235±0.0070</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5910±0.0000</t>
+          <t>0.5932±0.0114</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.6214±0.0089</t>
         </is>
       </c>
     </row>
